--- a/packages/xlsx/test-fixtures/defined-names.xlsx
+++ b/packages/xlsx/test-fixtures/defined-names.xlsx
@@ -7,6 +7,9 @@
   <definedNames>
     <definedName name="Rows">Data!$A$1:INDEX(Data!$A:$A,COUNTA(Data!$A:$A))</definedName>
     <definedName name="Header">SUM(Data!$1:$1)</definedName>
+    <definedName name="Spilled">SUM(Data!A1#)</definedName>
+    <definedName name="Picked">SUM(@Data!A1)</definedName>
+    <definedName name="Spaced">Data!A1: Data!B2</definedName>
   </definedNames>
 </workbook>
 </file>
